--- a/30_ETF_Construction_Management/instances/public_qqq_2026.xlsx
+++ b/30_ETF_Construction_Management/instances/public_qqq_2026.xlsx
@@ -1117,7 +1117,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1227,10 +1227,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1707,86 +1703,86 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="31" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="31" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="31" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="32" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="32" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="32" t="s">
         <v>278</v>
       </c>
     </row>
@@ -1852,216 +1848,216 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3665,222 +3661,222 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="19" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="19" t="n">
         <v>0.0238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="19" t="n">
         <v>0.023</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="19" t="n">
         <v>0.0197</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="19" t="n">
         <v>0.0196</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="19" t="n">
         <v>0.0183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="19" t="n">
         <v>0.0178</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="19" t="n">
         <v>0.0129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="19" t="n">
         <v>0.0127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="19" t="n">
         <v>0.0125</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="19" t="n">
         <v>0.0122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="19" t="n">
         <v>0.0119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="19" t="n">
         <v>0.0105</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="19" t="n">
         <v>0.0105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="19" t="n">
         <v>0.0098</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="19" t="n">
         <v>0.0092</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="19" t="n">
         <v>0.0091</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="19" t="n">
         <v>0.0088</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="19" t="n">
         <v>0.0085</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="19" t="n">
         <v>0.0085</v>
       </c>
     </row>
@@ -3897,9 +3893,9 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30" t="n">
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29" t="n">
         <f aca="false">SUM(D5:D35)</f>
         <v>1</v>
       </c>
@@ -3959,50 +3955,50 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="19" t="n">
         <v>0.029</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C46" s="28" t="n">
+      <c r="C46" s="19" t="n">
         <v>0.012</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C47" s="28" t="n">
+      <c r="C47" s="19" t="n">
         <v>0.011</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C48" s="28" t="n">
+      <c r="C48" s="19" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C49" s="28" t="n">
+      <c r="C49" s="19" t="n">
         <v>0.002</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C50" s="28" t="n">
+      <c r="C50" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4070,7 +4066,7 @@
       <c r="B6" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="30" t="n">
         <f aca="false">C5*Assumptions!$E$9</f>
         <v>35865000</v>
       </c>
@@ -4079,7 +4075,7 @@
       <c r="B7" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="30" t="n">
         <f aca="false">Assumptions!$E$8*Assumptions!$E$9</f>
         <v>35865000</v>
       </c>
@@ -4106,7 +4102,7 @@
       <c r="B10" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="30" t="n">
         <f aca="false">C9*C7</f>
         <v>0</v>
       </c>
